--- a/data/trans_orig/Q23-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q23-Estudios-trans_orig.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,57; 16,08</t>
+          <t>15,56; 16,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15,64; 16,23</t>
+          <t>15,65; 16,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15,72; 16,6</t>
+          <t>15,73; 16,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,89; 19,77</t>
+          <t>17,88; 19,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,77; 19,3</t>
+          <t>17,71; 19,31</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,71; 19,7</t>
+          <t>17,71; 20,01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,27; 16,88</t>
+          <t>16,29; 16,9</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>16,34; 16,95</t>
+          <t>16,3; 16,94</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16,43; 17,32</t>
+          <t>16,43; 17,28</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,37; 16,74</t>
+          <t>16,39; 16,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -802,32 +802,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16,67; 17,16</t>
+          <t>16,68; 17,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,09; 17,76</t>
+          <t>17,09; 17,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,27; 17,88</t>
+          <t>17,27; 17,85</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,48; 16,79</t>
+          <t>16,49; 16,79</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,76; 17,12</t>
+          <t>16,75; 17,1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16,79; 17,13</t>
+          <t>16,78; 17,14</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,91; 17,69</t>
+          <t>16,92; 17,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,11; 18,05</t>
+          <t>17,08; 18,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,66; 17,58</t>
+          <t>16,7; 17,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17,53; 18,87</t>
+          <t>17,53; 18,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17,28; 18,6</t>
+          <t>17,32; 18,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,83; 17,72</t>
+          <t>16,84; 17,73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,27; 18,02</t>
+          <t>17,26; 17,98</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17,31; 18,11</t>
+          <t>17,31; 18,07</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16,84; 17,5</t>
+          <t>16,87; 17,47</t>
         </is>
       </c>
     </row>
@@ -1007,37 +1007,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,19; 16,51</t>
+          <t>16,19; 16,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,32; 16,6</t>
+          <t>16,32; 16,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,33; 16,69</t>
+          <t>16,29; 16,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,21; 17,74</t>
+          <t>17,2; 17,75</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,41; 17,97</t>
+          <t>17,38; 17,95</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,41; 17,92</t>
+          <t>17,4; 17,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,64; 16,91</t>
+          <t>16,62; 16,89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,82; 17,13</t>
+          <t>16,8; 17,11</t>
         </is>
       </c>
     </row>
